--- a/datos_limpios/arg_tasas_est.xlsx
+++ b/datos_limpios/arg_tasas_est.xlsx
@@ -468,31 +468,31 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>688.45461793049412</v>
+        <v>689.11685203734305</v>
       </c>
       <c r="D2">
-        <v>674.71955722677251</v>
+        <v>675.3770053455637</v>
       </c>
       <c r="E2">
-        <v>702.25571315203581</v>
+        <v>702.92806404217367</v>
       </c>
       <c r="F2">
-        <v>1116.678698710391</v>
+        <v>892.80519422761358</v>
       </c>
       <c r="G2">
-        <v>994.20301570177662</v>
+        <v>795.96445377438977</v>
       </c>
       <c r="H2">
-        <v>1236.5320075854711</v>
+        <v>988.60292896356293</v>
       </c>
       <c r="I2">
-        <v>1805.0214416435319</v>
+        <v>1582.1818697800829</v>
       </c>
       <c r="J2">
-        <v>1682.2844488660321</v>
+        <v>1483.7034644550099</v>
       </c>
       <c r="K2">
-        <v>1926.148774516987</v>
+        <v>1678.9078126301331</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -503,31 +503,31 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>591.77295941314696</v>
+        <v>589.54143964407774</v>
       </c>
       <c r="D3">
-        <v>579.18348131492428</v>
+        <v>576.98843569586359</v>
       </c>
       <c r="E3">
-        <v>604.43641742185264</v>
+        <v>602.13564727561334</v>
       </c>
       <c r="F3">
-        <v>1299.2298679157841</v>
+        <v>835.68916238381985</v>
       </c>
       <c r="G3">
-        <v>1204.912999209296</v>
+        <v>774.53541615574738</v>
       </c>
       <c r="H3">
-        <v>1394.7517572492541</v>
+        <v>896.86790488691361</v>
       </c>
       <c r="I3">
-        <v>1891.0423236461099</v>
+        <v>1425.3452840707459</v>
       </c>
       <c r="J3">
-        <v>1794.868886821544</v>
+        <v>1363.294754780695</v>
       </c>
       <c r="K3">
-        <v>1987.933020552613</v>
+        <v>1488.2815906921619</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -538,31 +538,31 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>543.08497822786251</v>
+        <v>543.36552404865188</v>
       </c>
       <c r="D4">
-        <v>531.34246997001344</v>
+        <v>531.61860307171071</v>
       </c>
       <c r="E4">
-        <v>554.55342217570455</v>
+        <v>554.83753848081597</v>
       </c>
       <c r="F4">
-        <v>1295.6562008873821</v>
+        <v>1318.7815204398539</v>
       </c>
       <c r="G4">
-        <v>1173.235404490166</v>
+        <v>1190.142452633226</v>
       </c>
       <c r="H4">
-        <v>1413.542580068894</v>
+        <v>1443.2981729995131</v>
       </c>
       <c r="I4">
-        <v>1838.5040276813161</v>
+        <v>1862.3020258251861</v>
       </c>
       <c r="J4">
-        <v>1716.0030403322039</v>
+        <v>1732.1957132876739</v>
       </c>
       <c r="K4">
-        <v>1956.895334996703</v>
+        <v>1987.3372193764239</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -573,31 +573,31 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>528.44598751537023</v>
+        <v>529.2377748479546</v>
       </c>
       <c r="D5">
-        <v>517.31895880143816</v>
+        <v>518.1033149889488</v>
       </c>
       <c r="E5">
-        <v>539.54382033299362</v>
+        <v>540.34676130967853</v>
       </c>
       <c r="F5">
-        <v>1492.288106131952</v>
+        <v>1487.8003209611691</v>
       </c>
       <c r="G5">
-        <v>1384.3014564387281</v>
+        <v>1379.22265954205</v>
       </c>
       <c r="H5">
-        <v>1601.3777914697171</v>
+        <v>1596.5807177487229</v>
       </c>
       <c r="I5">
-        <v>2020.930157406912</v>
+        <v>2017.239671808278</v>
       </c>
       <c r="J5">
-        <v>1912.895567625357</v>
+        <v>1909.3217691995819</v>
       </c>
       <c r="K5">
-        <v>2129.8450083147109</v>
+        <v>2126.1593680605579</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -608,31 +608,31 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>753.4935218590233</v>
+        <v>754.70388739369696</v>
       </c>
       <c r="D6">
-        <v>739.12976312267415</v>
+        <v>740.32908113706389</v>
       </c>
       <c r="E6">
-        <v>768.47626270533124</v>
+        <v>769.69901874361301</v>
       </c>
       <c r="F6">
-        <v>1644.5902465505351</v>
+        <v>1228.371371260982</v>
       </c>
       <c r="G6">
-        <v>1402.7933459673709</v>
+        <v>1075.459435733894</v>
       </c>
       <c r="H6">
-        <v>1890.692767590012</v>
+        <v>1381.7287703115001</v>
       </c>
       <c r="I6">
-        <v>2398.444718852224</v>
+        <v>1982.9490313138081</v>
       </c>
       <c r="J6">
-        <v>2155.5127468722349</v>
+        <v>1828.5670563658209</v>
       </c>
       <c r="K6">
-        <v>2642.3853490890419</v>
+        <v>2135.9957325415171</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -643,31 +643,31 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>635.403676930134</v>
+        <v>634.73891472358946</v>
       </c>
       <c r="D7">
-        <v>622.03560657293406</v>
+        <v>621.3898724673121</v>
       </c>
       <c r="E7">
-        <v>648.75684765454912</v>
+        <v>648.05756677842237</v>
       </c>
       <c r="F7">
-        <v>1736.540073372784</v>
+        <v>1166.160421307462</v>
       </c>
       <c r="G7">
-        <v>1569.046848208046</v>
+        <v>1042.439367312295</v>
       </c>
       <c r="H7">
-        <v>1900.639093363578</v>
+        <v>1288.555897293593</v>
       </c>
       <c r="I7">
-        <v>2372.0993800971978</v>
+        <v>1801.278858255057</v>
       </c>
       <c r="J7">
-        <v>2202.2574410743769</v>
+        <v>1676.1762853597229</v>
       </c>
       <c r="K7">
-        <v>2536.3624565035302</v>
+        <v>1923.2401584761831</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -678,31 +678,31 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>613.41206263424942</v>
+        <v>614.32227758764702</v>
       </c>
       <c r="D8">
-        <v>600.84710108979971</v>
+        <v>601.75047214266021</v>
       </c>
       <c r="E8">
-        <v>625.98461311849223</v>
+        <v>626.91052142643809</v>
       </c>
       <c r="F8">
-        <v>1580.067499932255</v>
+        <v>1701.3913803824721</v>
       </c>
       <c r="G8">
-        <v>1407.6231999591921</v>
+        <v>1517.270302713365</v>
       </c>
       <c r="H8">
-        <v>1756.4252578861331</v>
+        <v>1888.6913604570921</v>
       </c>
       <c r="I8">
-        <v>2194.1245595210771</v>
+        <v>2315.7113421543932</v>
       </c>
       <c r="J8">
-        <v>2021.2927163327199</v>
+        <v>2130.62485423415</v>
       </c>
       <c r="K8">
-        <v>2369.770161229063</v>
+        <v>2503.115152750906</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -713,31 +713,31 @@
         <v>13</v>
       </c>
       <c r="C9">
-        <v>638.08332887830829</v>
+        <v>638.45773506420369</v>
       </c>
       <c r="D9">
-        <v>625.70712772452009</v>
+        <v>626.07936847007909</v>
       </c>
       <c r="E9">
-        <v>650.11916264802494</v>
+        <v>650.49875937619493</v>
       </c>
       <c r="F9">
-        <v>2133.329477490297</v>
+        <v>2399.8242031285199</v>
       </c>
       <c r="G9">
-        <v>1932.0830561334999</v>
+        <v>2182.3661028378019</v>
       </c>
       <c r="H9">
-        <v>2331.4857581454048</v>
+        <v>2613.1627202183731</v>
       </c>
       <c r="I9">
-        <v>2771.3909495428588</v>
+        <v>3038.1992486268459</v>
       </c>
       <c r="J9">
-        <v>2570.8963814562462</v>
+        <v>2821.2848714290121</v>
       </c>
       <c r="K9">
-        <v>2969.943154439612</v>
+        <v>3251.5686322121769</v>
       </c>
     </row>
   </sheetData>
